--- a/ingress-workflow_examples/animal/Rosy/NORT_R2/result/nort.xlsx
+++ b/ingress-workflow_examples/animal/Rosy/NORT_R2/result/nort.xlsx
@@ -7,16 +7,279 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="TrainingFamiliarization" sheetId="1" r:id="rId1"/>
+    <sheet name="TestNovelty" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="83">
+  <si>
+    <t>FamiliarNoseProximity</t>
+  </si>
+  <si>
+    <t>FamiliarNoseToObjectRay</t>
+  </si>
+  <si>
+    <t>FamiliarOlfactionResult</t>
+  </si>
+  <si>
+    <t>VariableNoseProximity</t>
+  </si>
+  <si>
+    <t>VariableNoseToObjectRay</t>
+  </si>
+  <si>
+    <t>VariableOlfactionResult</t>
+  </si>
+  <si>
+    <t>FamiliarCenterEarProximityFamiliar</t>
+  </si>
+  <si>
+    <t>FamiliarBaseTailProximity</t>
+  </si>
+  <si>
+    <t>FamiliarBodyProximityResult</t>
+  </si>
+  <si>
+    <t>VariableCenterEarProximityVariable</t>
+  </si>
+  <si>
+    <t>VariableBaseTailProximity</t>
+  </si>
+  <si>
+    <t>VariableBodyProximityResult</t>
+  </si>
+  <si>
+    <t>FamiliarLeftwardProxFOV</t>
+  </si>
+  <si>
+    <t>FamiliarRightwardProxFOV</t>
+  </si>
+  <si>
+    <t>FamiliarWhiskerInteractionResult</t>
+  </si>
+  <si>
+    <t>VariableLeftwardProxFOV</t>
+  </si>
+  <si>
+    <t>VariableRightwardProxFOV</t>
+  </si>
+  <si>
+    <t>VariableWhiskerInteractionResult</t>
+  </si>
+  <si>
+    <t>AbsoluteDiscriminationVariableFamiliar</t>
+  </si>
+  <si>
+    <t>AbsoluteDiscriminationFamiliarVariable</t>
+  </si>
+  <si>
+    <t>BiasScoreVariable</t>
+  </si>
+  <si>
+    <t>BiasScoreFamiliar</t>
+  </si>
+  <si>
+    <t>AbsoluteBiasScoreVariable</t>
+  </si>
+  <si>
+    <t>AbsoluteBiasScoreFamiliar</t>
+  </si>
+  <si>
+    <t>TotalObservationInstances</t>
+  </si>
+  <si>
+    <t>TotalSecondsObserving</t>
+  </si>
+  <si>
+    <t>SecondsObservingVariable</t>
+  </si>
+  <si>
+    <t>SecondsObservingFamiliar</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'Displacement')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'MedianSpeed')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'MedianAcceleration')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'FreezingTime')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'Entries')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 1)', 'SecondsPresent')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'Displacement')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'MedianSpeed')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'MedianAcceleration')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'FreezingTime')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'Entries')</t>
+  </si>
+  <si>
+    <t>('Quadrant(1, 2)', 'SecondsPresent')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'Displacement')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'MedianSpeed')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'MedianAcceleration')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'FreezingTime')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'Entries')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 1)', 'SecondsPresent')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'Displacement')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'MedianSpeed')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'MedianAcceleration')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'FreezingTime')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'Entries')</t>
+  </si>
+  <si>
+    <t>('Quadrant(2, 2)', 'SecondsPresent')</t>
+  </si>
+  <si>
+    <t>('All', 'Displacement')</t>
+  </si>
+  <si>
+    <t>('All', 'MedianSpeed')</t>
+  </si>
+  <si>
+    <t>('All', 'MedianAcceleration')</t>
+  </si>
+  <si>
+    <t>('All', 'FreezingTime')</t>
+  </si>
+  <si>
+    <t>('Reader', 'RawFrames')</t>
+  </si>
+  <si>
+    <t>('Reader', 'AugmentedFrames')</t>
+  </si>
+  <si>
+    <t>('Reader', 'DurationSeconds')</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Gene</t>
+  </si>
+  <si>
+    <t>Cohort</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>OO670_0</t>
+  </si>
+  <si>
+    <t>[False False False ... False False False]</t>
+  </si>
+  <si>
+    <t>OO670</t>
+  </si>
+  <si>
+    <t>MNK1</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>NovelNoseProximity</t>
+  </si>
+  <si>
+    <t>NovelNoseToObjectRay</t>
+  </si>
+  <si>
+    <t>NovelOlfactionResult</t>
+  </si>
+  <si>
+    <t>NovelCenterEarProximityNovel</t>
+  </si>
+  <si>
+    <t>NovelBaseTailProximity</t>
+  </si>
+  <si>
+    <t>NovelBodyProximityResult</t>
+  </si>
+  <si>
+    <t>NovelLeftwardProxFOV</t>
+  </si>
+  <si>
+    <t>NovelRightwardProxFOV</t>
+  </si>
+  <si>
+    <t>NovelWhiskerInteractionResult</t>
+  </si>
+  <si>
+    <t>AbsoluteDiscriminationNovelFamiliar</t>
+  </si>
+  <si>
+    <t>AbsoluteDiscriminationFamiliarNovel</t>
+  </si>
+  <si>
+    <t>BiasScoreNovel</t>
+  </si>
+  <si>
+    <t>AbsoluteBiasScoreNovel</t>
+  </si>
+  <si>
+    <t>SecondsObservingNovel</t>
+  </si>
+  <si>
+    <t>OO670_1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -32,7 +295,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,12 +303,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +621,790 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:64">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:64">
+      <c r="A2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2">
+        <v>10.07673333333333</v>
+      </c>
+      <c r="C2">
+        <v>132.9328</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2">
+        <v>15.3153</v>
+      </c>
+      <c r="F2">
+        <v>150.2501</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2">
+        <v>6.940266666666667</v>
+      </c>
+      <c r="I2">
+        <v>1.067733333333333</v>
+      </c>
+      <c r="J2">
+        <v>7.841166666666667</v>
+      </c>
+      <c r="K2">
+        <v>14.68133333333333</v>
+      </c>
+      <c r="L2">
+        <v>8.008000000000001</v>
+      </c>
+      <c r="M2">
+        <v>17.65096666666667</v>
+      </c>
+      <c r="N2">
+        <v>2.035366666666667</v>
+      </c>
+      <c r="O2">
+        <v>3.970633333333333</v>
+      </c>
+      <c r="P2">
+        <v>4.9049</v>
+      </c>
+      <c r="Q2">
+        <v>3.236566666666667</v>
+      </c>
+      <c r="R2">
+        <v>9.342666666666666</v>
+      </c>
+      <c r="S2">
+        <v>11.57823333333333</v>
+      </c>
+      <c r="T2">
+        <v>6.673333333333333</v>
+      </c>
+      <c r="U2">
+        <v>6.673333333333333</v>
+      </c>
+      <c r="V2">
+        <v>70.24291497975709</v>
+      </c>
+      <c r="W2">
+        <v>29.75708502024291</v>
+      </c>
+      <c r="X2">
+        <v>3.891006952231442</v>
+      </c>
+      <c r="Y2">
+        <v>1.648351648351648</v>
+      </c>
+      <c r="Z2">
+        <v>11</v>
+      </c>
+      <c r="AA2">
+        <v>16.48313333333333</v>
+      </c>
+      <c r="AB2">
+        <v>11.57823333333333</v>
+      </c>
+      <c r="AC2">
+        <v>4.9049</v>
+      </c>
+      <c r="AD2">
+        <v>1.850930889991525</v>
+      </c>
+      <c r="AE2">
+        <v>0.07616987073042344</v>
+      </c>
+      <c r="AF2">
+        <v>0.07662630414410095</v>
+      </c>
+      <c r="AG2">
+        <v>2.736066666666667</v>
+      </c>
+      <c r="AH2">
+        <v>5</v>
+      </c>
+      <c r="AI2">
+        <v>19.7197</v>
+      </c>
+      <c r="AJ2">
+        <v>2.821984895560878</v>
+      </c>
+      <c r="AK2">
+        <v>0.03007080563521332</v>
+      </c>
+      <c r="AL2">
+        <v>0.02363919670788448</v>
+      </c>
+      <c r="AM2">
+        <v>13.4134</v>
+      </c>
+      <c r="AN2">
+        <v>4</v>
+      </c>
+      <c r="AO2">
+        <v>51.5515</v>
+      </c>
+      <c r="AP2">
+        <v>5.229637118957939</v>
+      </c>
+      <c r="AQ2">
+        <v>0.02311630823539809</v>
+      </c>
+      <c r="AR2">
+        <v>0.01720819903176403</v>
+      </c>
+      <c r="AS2">
+        <v>33.70033333333334</v>
+      </c>
+      <c r="AT2">
+        <v>8</v>
+      </c>
+      <c r="AU2">
+        <v>139.9731666666667</v>
+      </c>
+      <c r="AV2">
+        <v>1.588353609795645</v>
+      </c>
+      <c r="AW2">
+        <v>0.02062327219533314</v>
+      </c>
+      <c r="AX2">
+        <v>0.01906429873445743</v>
+      </c>
+      <c r="AY2">
+        <v>16.4164</v>
+      </c>
+      <c r="AZ2">
+        <v>4</v>
+      </c>
+      <c r="BA2">
+        <v>45.97926666666667</v>
+      </c>
+      <c r="BB2">
+        <v>15.90458927479053</v>
+      </c>
+      <c r="BC2">
+        <v>0.02588485361531911</v>
+      </c>
+      <c r="BD2">
+        <v>0.01739580507178418</v>
+      </c>
+      <c r="BE2">
+        <v>69.23583333333333</v>
+      </c>
+      <c r="BF2">
+        <v>8992</v>
+      </c>
+      <c r="BG2">
+        <v>8918</v>
+      </c>
+      <c r="BH2">
+        <v>297.5639333333334</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK2">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BL2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:64">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:64">
+      <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2">
+        <v>4.938683676268862</v>
+      </c>
+      <c r="C2">
+        <v>154.4006038520002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2">
+        <v>6.440310469728988</v>
+      </c>
+      <c r="F2">
+        <v>156.4695118785452</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2">
+        <v>4.171185537389241</v>
+      </c>
+      <c r="I2">
+        <v>0.2335863900937975</v>
+      </c>
+      <c r="J2">
+        <v>4.171185537389241</v>
+      </c>
+      <c r="K2">
+        <v>6.006507173840507</v>
+      </c>
+      <c r="L2">
+        <v>1.368148856263671</v>
+      </c>
+      <c r="M2">
+        <v>6.473679954028102</v>
+      </c>
+      <c r="N2">
+        <v>2.769667196826456</v>
+      </c>
+      <c r="O2">
+        <v>2.20238596374152</v>
+      </c>
+      <c r="P2">
+        <v>3.73738224150076</v>
+      </c>
+      <c r="Q2">
+        <v>2.235755448040633</v>
+      </c>
+      <c r="R2">
+        <v>2.669558743929114</v>
+      </c>
+      <c r="S2">
+        <v>3.804121210098988</v>
+      </c>
+      <c r="T2">
+        <v>0.06673896859822781</v>
+      </c>
+      <c r="U2">
+        <v>0.06673896859822781</v>
+      </c>
+      <c r="V2">
+        <v>50.4424778761062</v>
+      </c>
+      <c r="W2">
+        <v>49.5575221238938</v>
+      </c>
+      <c r="X2">
+        <v>1.658181818181818</v>
+      </c>
+      <c r="Y2">
+        <v>1.629090909090909</v>
+      </c>
+      <c r="Z2">
+        <v>7</v>
+      </c>
+      <c r="AA2">
+        <v>7.541503451599748</v>
+      </c>
+      <c r="AB2">
+        <v>3.804121210098988</v>
+      </c>
+      <c r="AC2">
+        <v>3.73738224150076</v>
+      </c>
+      <c r="AD2">
+        <v>1.818230679769389</v>
+      </c>
+      <c r="AE2">
+        <v>0.09073281431864495</v>
+      </c>
+      <c r="AF2">
+        <v>0.06739251777545471</v>
+      </c>
+      <c r="AG2">
+        <v>2.068908026545063</v>
+      </c>
+      <c r="AH2">
+        <v>3</v>
+      </c>
+      <c r="AI2">
+        <v>14.44898670151633</v>
+      </c>
+      <c r="AJ2">
+        <v>3.779431526515415</v>
+      </c>
+      <c r="AK2">
+        <v>0.009785833765611837</v>
+      </c>
+      <c r="AL2">
+        <v>0.006333614190635106</v>
+      </c>
+      <c r="AM2">
+        <v>92.93401377303229</v>
+      </c>
+      <c r="AN2">
+        <v>4</v>
+      </c>
+      <c r="AO2">
+        <v>172.8539286694102</v>
+      </c>
+      <c r="AP2">
+        <v>1.037217232291967</v>
+      </c>
+      <c r="AQ2">
+        <v>0.05243940920543449</v>
+      </c>
+      <c r="AR2">
+        <v>0.04615920026375885</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>5</v>
+      </c>
+      <c r="AU2">
+        <v>15.41670174619064</v>
+      </c>
+      <c r="AV2">
+        <v>0.775223033692901</v>
+      </c>
+      <c r="AW2">
+        <v>0.06705001299201456</v>
+      </c>
+      <c r="AX2">
+        <v>0.02658573509062394</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>3</v>
+      </c>
+      <c r="BA2">
+        <v>11.51247208319431</v>
+      </c>
+      <c r="BB2">
+        <v>10.51858390081211</v>
+      </c>
+      <c r="BC2">
+        <v>0.01421661006309977</v>
+      </c>
+      <c r="BD2">
+        <v>0.008954675007803004</v>
+      </c>
+      <c r="BE2">
+        <v>97.30541621621622</v>
+      </c>
+      <c r="BF2">
+        <v>8991</v>
+      </c>
+      <c r="BG2">
+        <v>6875</v>
+      </c>
+      <c r="BH2">
+        <v>229.4152045564083</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK2">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>